--- a/data_extactor/batch_10_fa/trimmed/batch_0025_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0025_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | علوم پایه | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | روان‌شناسی | آموزش و توانمندسازی | مدیریت و امور اداری | ریاضیات | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پرسنل و منابع انسانی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | ریاضیات | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مشاوران و راهنمایان تحصیلی و شغلی | مدیران منابع انسانی | کارشناسان منابع انسانی | تحلیل‌گران فرایندهای مدیریتی | استادان روان‌شناسی در دانشگاه | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>مشاوران تحصیلی، شغلی و هدایت استعدادها | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان تحلیل مدیریت و روش‌ها | استادان روان‌شناسی دانشگاه | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | آموزش و توانمندسازی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | مشاوران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | روان‌پزشکان | مشاوران توانبخشی | روان‌شناسان مدارس</t>
+          <t>پرستاران تخصصی روانپزشکی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | روان‌پزشکان | مشاوران توانبخشی | روان‌شناسان مدارس</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | آموزش و توانمندسازی | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی | امور حقوقی و دولتی</t>
+          <t>روان‌شناسی | درمان و مشاوره | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | قانون و دولت</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدارس | روان‌شناسان بالینی و سلامت روان | مشاوران و راهنمایان تحصیلی و شغلی | مشاوران سلامت روان | مشاوران توانبخشی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره متوسطه اول</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | مشاوران تحصیلی، شغلی و هدایت استعدادها | مشاوران سلامت روان | مشاوران توانبخشی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | آموزش و توانمندسازی | ریاضیات | خدمات مشتریان و خدمات فردی</t>
+          <t>روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و سلامت روان | روان‌شناسان مدارس | روان‌شناسان صنعتی و سازمانی | مشاوران ازدواج و خانواده | مشاوران سلامت روان | مشاوران و راهنمایان تحصیلی و شغلی | استادان روان‌شناسی در دانشگاه</t>
+          <t>روان‌شناسان بالینی و مشاوران سلامت روان | روان‌شناسان مدارس | روان‌شناسان صنعتی و سازمانی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران تحصیلی، شغلی و هدایت استعدادها | استادان روان‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | علوم پایه | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | آموزش و توانمندسازی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و مردم‌شناسی | زیست‌شناسی</t>
+          <t>روان‌شناسی | درمان و مشاوره | آموزش و پرورش | پزشکی و دندان‌پزشکی | جامعه‌شناسی و انسان‌شناسی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان عصب‌روان‌شناسی بالینی | روان‌شناسان بالینی و سلامت روان | مشاوران سلامت روان | متخصصان بیماری‌های مغز و اعصاب (نورولوژیست‌ها) | کاردرمانگران | روان‌پزشکان | روان‌شناسان مدارس</t>
+          <t>متخصصان عصب‌روان‌شناسی بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | مشاوران سلامت روان | متخصصان مغز و اعصاب | کاردرمانگران | روان‌پزشکان | روان‌شناسان مدارس</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | آموزش و توانمندسازی | پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی</t>
+          <t>روان‌شناسی | درمان و مشاوره | آموزش و پرورش | پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | روان‌شناسان بالینی و سلامت روان | متخصصان بیماری‌های مغز و اعصاب (نورولوژیست‌ها) | متخصصان عصب‌روان‌شناسی | کاردرمانگران | متخصصان طب فیزیکی و توانبخشی | روان‌پزشکان</t>
+          <t>پرستاران تخصصی روانپزشکی | روان‌شناسان بالینی و مشاوران سلامت روان | متخصصان مغز و اعصاب | متخصصان عصب‌روان‌شناسی | کاردرمانگران | متخصصان طب فیزیکی و توانبخشی | روان‌پزشکان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نگارش | درک مطلب | یادگیری فعال | تفکر انتقادی | استراتژی‌های یادگیری | نظارت | علوم پایه</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | آموزش و توانمندسازی | ریاضیات | تاریخ و باستان‌شناسی | امور حقوقی و دولتی | روان‌شناسی</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | ریاضیات | تاریخ و باستان‌شناسی | قانون و دولت | روان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بیان کتبی | استدلال استقرایی | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | استدلال استقرایی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | اقتصاددانان | تاریخ‌نگاران | دانشمندان علوم سیاسی | دستیاران پژوهشی علوم اجتماعی | استادان جامعه‌شناسی در دانشگاه | پژوهشگران نظرسنجی و پیمایش</t>
+          <t>انسان‌شناسان و باستان‌شناسان | اقتصاددانان | مورخان | دانشمندان و پژوهشگران علوم سیاسی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | استادان جامعه‌شناسی دانشگاه | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>امور حقوقی و دولتی | جغرافیا | ترابری و حمل‌ونقل | مدیریت و امور اداری | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک</t>
+          <t>قانون و دولت | جغرافیا | حمل و نقل | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>دانشمندان علوم حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست (شامل بهداشت محیط) | جغرافیدانان | معماران منظر | کارشناسان مدیریت پروژه | برنامه‌ریزان سیستم‌های حمل‌ونقل</t>
+          <t>دانشمندان حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | جغرافیدانان | مهندسان معمار منظر | کارشناسان مدیریت پروژه | برنامه‌ریزان سیستم‌های حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | تاریخ و باستان‌شناسی | زبان‌های خارجی | آموزش و توانمندسازی | جغرافیا | فلسفه و الهیات</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | زبان خارجی | آموزش و پرورش | جغرافیا | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان کتبی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>بیان کتبی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی در دانشگاه | کارشناسان اسناد و مدارک تاریخی و آرشیوداران | موزه‌داران | جغرافیدانان | تاریخ‌نگاران | دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | کارشناسان اسناد و آرشیو | موزه‌داران | جغرافیدانان | مورخان | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال | علوم پایه | استراتژی‌های یادگیری | نظارت | ریاضیات</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | علوم | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | زبان انگلیسی | رایانه و الکترونیک | آموزش و توانمندسازی | جامعه‌شناسی و مردم‌شناسی | ریاضیات</t>
+          <t>جغرافیا | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال استقرایی | درک شفاهی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | درک شفاهی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقشه‌نگاران و متخصصان فتوگرامتری | دانشمندان علوم حفاظت از منابع طبیعی | نقشه‌برداران ژئودتیک | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی GIS | دانشمندان علوم زمین (به‌جز هیدرولوژیست‌ها و جغرافیدانان) | متخصصان و دانشمندان سنجش از دور | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>کارشناسان نقشه‌نگاری و فتوگرامتری | دانشمندان حفاظت از منابع طبیعی | مهندسان نقشه‌برداری ژئودزی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | دانشمندان و فناوران سنجش از دور | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
